--- a/docs/LINEニュース配信ボット_設計書.xlsx
+++ b/docs/LINEニュース配信ボット_設計書.xlsx
@@ -2013,13 +2013,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>無料枠</t>
+          <t>無料枠（2026-07時点）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>public リポジトリは実質無制限</t>
+          <t>public リポジトリ＋標準ランナーは無制限・無料</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>3回/日</t>
+          <t>3回/日（cron）</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2073,20 +2073,21 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Groq API</t>
+          <t>Groq API
+(llama-3.3-70b-versatile)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>無料枠（1日1,000リクエスト目安）</t>
+          <t>30 RPM / 1,000 RPD / 12,000 TPM / 100,000 TPD</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>3リクエスト/日</t>
+          <t>約3リクエスト/日・1万トークン/日未満</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2103,7 +2104,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>月200通</t>
+          <t>コミュニケーションプラン：0円・200通/月</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2117,9 +2118,77 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>補足・注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Actions 注記</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>larger runner（非標準ランナー）は public でも課金対象。本ボットは標準ランナーのみ使用のため無料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Groq 実効制約</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>リクエスト数(1,000 RPD)より1日あたりトークン数(100,000 TPD)が実質的な上限。本ボットは3リクエスト/日・数千〜1万トークン/日程度のため大きく下回る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>LINE 料金改定</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>2026年10月1日より追加メッセージの料金体系が改定予定（20万通を境にした2段階）。ただし無料枠200通/月は維持され、本ボット（約90通/月）に影響なし。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>調査日</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-02 時点の各社公表情報に基づく。無料枠は変更され得るため定期的に確認すること。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A8:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/LINEニュース配信ボット_設計書.xlsx
+++ b/docs/LINEニュース配信ボット_設計書.xlsx
@@ -2073,7 +2073,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="50" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Groq API
@@ -2082,12 +2082,16 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>30 RPM / 1,000 RPD / 12,000 TPM / 100,000 TPD</t>
+          <t>1,000 リクエスト/日
+100,000 トークン/日
+（30 リクエスト/分・12,000 トークン/分）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>約3リクエスト/日・1万トークン/日未満</t>
+          <t>約 3 リクエスト/日
+約 1万 トークン/日 未満
+（1回の実行で 1 リクエスト）</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2157,7 +2161,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>リクエスト数(1,000 RPD)より1日あたりトークン数(100,000 TPD)が実質的な上限。本ボットは3リクエスト/日・数千〜1万トークン/日程度のため大きく下回る。</t>
+          <t>「1,000 リクエスト/日」より「100,000 トークン/日」の方が実質的な上限。本ボットは3リクエスト/日・数千〜1万トークン/日程度のため大きく下回る。（RPM/RPD/TPM/TPD＝1分/1日あたりのリクエスト数・トークン数）</t>
         </is>
       </c>
     </row>

--- a/docs/LINEニュース配信ボット_設計書.xlsx
+++ b/docs/LINEニュース配信ボット_設計書.xlsx
@@ -924,7 +924,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1日3回：07:00 / 12:00 / 18:00（JST）</t>
+          <t>1日3回：07:30 / 12:00 / 18:00（JST）</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1890,12 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>0 22 * * *</t>
+          <t>30 22 * * *</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">

--- a/docs/LINEニュース配信ボット_設計書.xlsx
+++ b/docs/LINEニュース配信ボット_設計書.xlsx
@@ -924,7 +924,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1日3回：07:30 / 12:00 / 18:00（JST）</t>
+          <t>1日3回：07:37 / 12:07 / 17:53（JST）</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1890,12 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>30 22 * * *</t>
+          <t>37 22 * * *</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1907,12 +1907,12 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>0 3 * * *</t>
+          <t>7 3 * * *</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1924,12 +1924,12 @@
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>0 9 * * *</t>
+          <t>53 8 * * *</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>GitHub Actions の cron は数分〜十数分の遅延が生じる場合がある（仕様）。</t>
+          <t>GitHub Actions の cron は高負荷時に遅延・スキップが生じる場合がある（仕様）。毎時 :00 は最も混雑するため、配信時刻は :00 を避けた分（例: 07:37 / 12:07 / 17:53 JST）に設定している。</t>
         </is>
       </c>
     </row>

--- a/docs/LINEニュース配信ボット_設計書.xlsx
+++ b/docs/LINEニュース配信ボット_設計書.xlsx
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>fetch_articles(): 複数RSSを取得し、直近HOURS_WINDOW時間・タイトル重複除外で候補記事を作成。</t>
+          <t>fetch_articles(): 複数RSSを取得し、直近HOURS_WINDOW時間・タイトル重複除外で候補記事を作成。各記事の概要(description)もHTML除去して保持。</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>select_with_groq(): 候補タイトル一覧をGroqに渡し、重要TOP_N件をJSONで受領。記事番号(id)で元記事のタイトル・URLを紐付け。</t>
+          <t>select_with_groq(): 候補の「タイトル＋概要」をGroqに渡し、重要TOP_N件をJSONで受領。要約はタイトルの言い換えを避け概要に基づく（プロンプト指示）。記事番号(id)で元記事のタイトル・URLを紐付け。</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="66" customHeight="1">
+    <row r="4" ht="82" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>fetch_articles(feeds, hours_window)</t>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>記事リスト [{title, url}]</t>
+          <t>記事リスト [{title, url, desc}]</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1578,11 +1578,12 @@
           <t>・全フィードを順次取得
 ・直近 hours_window 時間の記事のみ（公開時刻がある記事に適用）
 ・タイトル重複を除外
+・概要(summary/description)をHTML除去し120字に整形して desc に保持
 ・1フィードが失敗しても残りを継続</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="66" customHeight="1">
+    <row r="5" ht="82" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>select_with_groq(articles, top_n, model_name)</t>
@@ -1600,8 +1601,9 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>・タイトル一覧をGroqへ送信（JSON強制: response_format=json_object）
+          <t>・「タイトル＋概要」をGroqへ送信（JSON強制: response_format=json_object）
 ・選定基準: 社会的影響・技術革新・ビジネスインパクト・速報性
+・要約は概要に基づき、タイトルの言い換え/繰り返しを避ける（プロンプト指示）
 ・返却された記事番号(id)で元記事のタイトル・URLを紐付け
 ・不正/範囲外/重複idは除外</t>
         </is>
